--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Knowledge_Hub/02.FOMD/02.metadata_structure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24C69B1-1CFD-4952-B9CC-BA1C8B5EE42B}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF3B935-AB4D-421E-B02A-87F357665416}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>rule</t>
   </si>
   <si>
-    <t>if a study provide for example costs by each year (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (20112014)</t>
-  </si>
-  <si>
     <t>biodiversity</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule apply also for biodiversity measured at different stages of crop emergence, for example.</t>
+  </si>
+  <si>
+    <t>if a study provide for example costs by each year (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
   </si>
 </sst>
 </file>
@@ -441,6 +441,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="159.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -456,23 +457,23 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -481,6 +482,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -675,27 +696,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C37792-64C1-463D-9685-059A0C240F70}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -712,23 +732,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF3B935-AB4D-421E-B02A-87F357665416}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A56A341C-8709-4F1D-9F97-A61DA50B5EF9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>outcome_type</t>
   </si>
@@ -57,13 +57,37 @@
   </si>
   <si>
     <t>if a study provide for example costs by each year (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>if the study provide agregated results complete location in one row, if provide results by location, one row per location</t>
+  </si>
+  <si>
+    <t>location\</t>
+  </si>
+  <si>
+    <t>for checking geographic location points or converting them to decimals use: https://rcn.montana.edu/Resources/Converter.aspx</t>
+  </si>
+  <si>
+    <t>yield</t>
+  </si>
+  <si>
+    <t>for intercropping systems prioritize the inclusion of LER</t>
+  </si>
+  <si>
+    <t>YIELD</t>
+  </si>
+  <si>
+    <t>if study provide yield for different years, extract for each year separately</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +99,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -100,9 +131,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,14 +469,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2520CDD-996F-47C9-A5A9-875181618DDD}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="159.85546875" customWidth="1"/>
+    <col min="2" max="2" width="159.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -460,7 +492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -468,12 +500,44 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -482,6 +546,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -492,18 +565,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -522,6 +586,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -579,6 +644,11 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -697,6 +767,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -707,29 +785,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C37792-64C1-463D-9685-059A0C240F70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}"/>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A56A341C-8709-4F1D-9F97-A61DA50B5EF9}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{695DE79A-E47F-44FA-A96C-AC3242127E03}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
+    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>outcome_type</t>
   </si>
@@ -50,44 +50,38 @@
     <t>biodiversity</t>
   </si>
   <si>
-    <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and aggregated abundance (2011-2014) we record the aggreated one only (20112014)</t>
-  </si>
-  <si>
     <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule apply also for biodiversity measured at different stages of crop emergence, for example.</t>
   </si>
   <si>
-    <t>if a study provide for example costs by each year (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
-    <t>if the study provide agregated results complete location in one row, if provide results by location, one row per location</t>
-  </si>
-  <si>
-    <t>location\</t>
-  </si>
-  <si>
-    <t>for checking geographic location points or converting them to decimals use: https://rcn.montana.edu/Resources/Converter.aspx</t>
-  </si>
-  <si>
     <t>yield</t>
   </si>
   <si>
     <t>for intercropping systems prioritize the inclusion of LER</t>
   </si>
   <si>
-    <t>YIELD</t>
-  </si>
-  <si>
-    <t>if study provide yield for different years, extract for each year separately</t>
+    <t>if a study provide yield for multiple years (2011,2012,2013,2014) and aggregated yield (2011-2014) we record yield for each year (2011,2012,2013,2014) separately</t>
+  </si>
+  <si>
+    <t>if a study provide for example costs by for multiple years (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
+  </si>
+  <si>
+    <t>if a study provide for example abundance for multiple years (2011,2012,2013,2014) and aggregated abundance (2011-2014) we record the aggreated one only (20112014)</t>
+  </si>
+  <si>
+    <t>To check, validate, or convert coordinates into decimal format, use: https://rcn.montana.edu/Resources/Converter.aspx</t>
+  </si>
+  <si>
+    <t>If the study reports aggregated results, enter the location once in a single row. If results are reported for multiple locations or outcomes, create one row per location per outcome.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +100,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -131,10 +131,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,13 +471,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2520CDD-996F-47C9-A5A9-875181618DDD}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="159.81640625" customWidth="1"/>
+    <col min="2" max="2" width="159.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,15 +485,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -500,72 +501,55 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B8">
+    <sortCondition ref="A2:A8"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -766,10 +750,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -786,5 +801,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,21 +41,33 @@
     <t>outcome_type</t>
   </si>
   <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>biodiversity</t>
+  </si>
+  <si>
+    <t>if a study provide for example abundance for multiple years (2011,2012,2013,2014) and aggregated abundance (2011-2014) we record the aggreated one only (20112014)</t>
+  </si>
+  <si>
+    <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule apply also for biodiversity measured at different stages of crop emergence, for example.</t>
+  </si>
+  <si>
     <t>economic</t>
   </si>
   <si>
-    <t>rule</t>
-  </si>
-  <si>
-    <t>biodiversity</t>
-  </si>
-  <si>
-    <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule apply also for biodiversity measured at different stages of crop emergence, for example.</t>
+    <t>if a study provide for example costs by for multiple years (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
   </si>
   <si>
     <t>location</t>
   </si>
   <si>
+    <t>If the study reports aggregated results, enter the location once in a single row. If results are reported for multiple locations or outcomes, create one row per location per outcome.</t>
+  </si>
+  <si>
+    <t>To check, validate, or convert coordinates into decimal format, use: https://rcn.montana.edu/Resources/Converter.aspx</t>
+  </si>
+  <si>
     <t>yield</t>
   </si>
   <si>
@@ -63,25 +75,13 @@
   </si>
   <si>
     <t>if a study provide yield for multiple years (2011,2012,2013,2014) and aggregated yield (2011-2014) we record yield for each year (2011,2012,2013,2014) separately</t>
-  </si>
-  <si>
-    <t>if a study provide for example costs by for multiple years (2011,2012,2013,2014) and aggregated cost (2011-2014) we record the aggreated one only (2011-2014)</t>
-  </si>
-  <si>
-    <t>if a study provide for example abundance for multiple years (2011,2012,2013,2014) and aggregated abundance (2011-2014) we record the aggreated one only (20112014)</t>
-  </si>
-  <si>
-    <t>To check, validate, or convert coordinates into decimal format, use: https://rcn.montana.edu/Resources/Converter.aspx</t>
-  </si>
-  <si>
-    <t>If the study reports aggregated results, enter the location once in a single row. If results are reported for multiple locations or outcomes, create one row per location per outcome.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,74 +471,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2520CDD-996F-47C9-A5A9-875181618DDD}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="159.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -751,6 +751,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -761,49 +770,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}"/>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{695DE79A-E47F-44FA-A96C-AC3242127E03}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E47964B0-F95E-492E-96B2-D75D263619EF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
@@ -751,15 +751,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -770,14 +761,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}"/>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E47964B0-F95E-492E-96B2-D75D263619EF}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E6428C-3542-4B14-99C8-430FB5445B27}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>outcome_type</t>
   </si>
@@ -75,13 +75,16 @@
   </si>
   <si>
     <t>if a study provide yield for multiple years (2011,2012,2013,2014) and aggregated yield (2011-2014) we record yield for each year (2011,2012,2013,2014) separately</t>
+  </si>
+  <si>
+    <t>if a study provide for example cost by each year (2011,2012,2013,2014) and does not provide aggregated cost, we record cost for each year (2011,2012,2013,2014) separately</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,14 +473,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2520CDD-996F-47C9-A5A9-875181618DDD}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="159.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,7 +488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -493,7 +496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -501,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -509,47 +512,64 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B8">
-    <sortCondition ref="A2:A8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B9">
+    <sortCondition ref="A2:A9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -750,7 +770,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -761,23 +781,40 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E6428C-3542-4B14-99C8-430FB5445B27}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{8E073767-A64B-4B5E-AA1A-FE4AF8EA9566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF1FF5DA-37E1-4B54-8400-8FC97951AFF2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{92072C7B-8E20-4DE1-95C7-166B6F9C1279}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>if a study provide for example abundance for multiple years (2011,2012,2013,2014) and aggregated abundance (2011-2014) we record the aggreated one only (20112014)</t>
   </si>
   <si>
-    <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule apply also for biodiversity measured at different stages of crop emergence, for example.</t>
-  </si>
-  <si>
     <t>economic</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>if a study provide for example cost by each year (2011,2012,2013,2014) and does not provide aggregated cost, we record cost for each year (2011,2012,2013,2014) separately</t>
+  </si>
+  <si>
+    <t>if a study provide for example abundance by each year (2011,2012,2013,2014) and does not provide aggregated abundance, we record abundance for the last year only (2014). This rule dont apply  for biodiversity measured at different stages of crop emergence, for example if a study provides biodiversity for vegetative, grain filling and harvest, we  record biodiversity at each stage separately.</t>
   </si>
 </sst>
 </file>
@@ -474,13 +474,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2520CDD-996F-47C9-A5A9-875181618DDD}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="159.85546875" customWidth="1"/>
+    <col min="2" max="2" width="159.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -496,60 +496,60 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -561,15 +561,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -770,6 +761,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -782,14 +782,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -808,6 +800,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
   <ds:schemaRefs>

--- a/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/05_FOMD_extraction_criteria.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -561,6 +561,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -761,15 +770,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -782,6 +782,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69B8806-DDE0-4888-A9BA-99D3068C5D78}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -800,14 +808,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F1267-8BEB-45FE-860C-4F0258A7DEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E68CB0-6E16-4675-BC2D-AC62A7116673}">
   <ds:schemaRefs>
